--- a/アイデア.xlsx
+++ b/アイデア.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HigutiHaruyuki\Documents\GitHub\Fugedaku_TeamKagoshima\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FCDD953-CEC9-4C9A-8164-ECA49A2269C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F19B5D23-144D-412E-B7F0-09ED28959438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-255" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
